--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Gear5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A74C2633-D8A0-4219-BF17-33E40DDE7F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C56758-8EAA-4692-ADB8-DD0BA546EABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="10845" xr2:uid="{106B1765-38FE-4447-9183-9ED041E46009}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="68">
   <si>
     <t>Stop #</t>
   </si>
@@ -225,13 +225,31 @@
   </si>
   <si>
     <t>TIME</t>
+  </si>
+  <si>
+    <t>RS Software</t>
+  </si>
+  <si>
+    <t>Philips More</t>
+  </si>
+  <si>
+    <t>Narkel Bagan</t>
+  </si>
+  <si>
+    <t>Unitech Gate 2</t>
+  </si>
+  <si>
+    <t>TCS Gitanjali</t>
+  </si>
+  <si>
+    <t>Ecospace</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,6 +274,19 @@
       <b/>
       <sz val="13.5"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF007B8B"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
+      <color rgb="FF007B8B"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -295,7 +326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
@@ -315,6 +346,8 @@
     <xf numFmtId="18" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -655,7 +688,7 @@
     <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.5703125" bestFit="1" customWidth="1"/>
@@ -1237,12 +1270,21 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C22" s="5">
+    <row r="22" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
         <v>20</v>
       </c>
-      <c r="D22" t="s">
-        <v>44</v>
+      <c r="D22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="3">
+        <v>22.576878000000001</v>
+      </c>
+      <c r="F22" s="3">
+        <v>88.434791000000004</v>
+      </c>
+      <c r="G22" s="6">
+        <v>0.35902777777777778</v>
       </c>
       <c r="I22" s="5">
         <v>20</v>
@@ -1257,12 +1299,21 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C23" s="5">
+    <row r="23" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
         <v>21</v>
       </c>
-      <c r="D23" t="s">
-        <v>45</v>
+      <c r="D23" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="3">
+        <v>22.578410000000002</v>
+      </c>
+      <c r="F23" s="3">
+        <v>88.435537999999994</v>
+      </c>
+      <c r="G23" s="6">
+        <v>0.36041666666666666</v>
       </c>
       <c r="I23" s="5">
         <v>21</v>
@@ -1277,12 +1328,21 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C24" s="5">
+    <row r="24" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
         <v>22</v>
       </c>
-      <c r="D24" t="s">
-        <v>46</v>
+      <c r="D24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="3">
+        <v>22.578506000000001</v>
+      </c>
+      <c r="F24" s="3">
+        <v>88.473668000000004</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0.36388888888888887</v>
       </c>
       <c r="I24" s="5">
         <v>22</v>
@@ -1297,12 +1357,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C25" s="5">
+    <row r="25" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
         <v>23</v>
       </c>
-      <c r="D25" t="s">
-        <v>47</v>
+      <c r="D25" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="3">
+        <v>22.577178</v>
+      </c>
+      <c r="F25" s="3">
+        <v>88.482962999999998</v>
+      </c>
+      <c r="G25" s="6">
+        <v>0.36805555555555558</v>
       </c>
       <c r="I25" s="5">
         <v>23</v>
@@ -1317,12 +1386,21 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C26" s="5">
+    <row r="26" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
         <v>24</v>
       </c>
-      <c r="D26" t="s">
-        <v>48</v>
+      <c r="D26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="3">
+        <v>22.580936999999999</v>
+      </c>
+      <c r="F26" s="3">
+        <v>88.487313</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0.37013888888888891</v>
       </c>
       <c r="I26" s="5">
         <v>24</v>
@@ -1337,12 +1415,21 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C27" s="5">
+    <row r="27" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
         <v>25</v>
       </c>
-      <c r="D27" t="s">
-        <v>49</v>
+      <c r="D27" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="3">
+        <v>22.585236999999999</v>
+      </c>
+      <c r="F27" s="3">
+        <v>88.488546999999997</v>
+      </c>
+      <c r="G27" s="6">
+        <v>0.37847222222222221</v>
       </c>
       <c r="I27" s="5">
         <v>25</v>
@@ -1374,6 +1461,7 @@
       </c>
     </row>
     <row r="30" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="E30" s="7"/>
       <c r="L30" s="5">
         <v>28</v>
       </c>
@@ -1382,6 +1470,7 @@
       </c>
     </row>
     <row r="31" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="E31" s="7"/>
       <c r="L31" s="5">
         <v>29</v>
       </c>
@@ -1397,7 +1486,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E33" s="8"/>
       <c r="L33" s="5">
         <v>31</v>
       </c>
@@ -1407,5 +1497,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>